--- a/src/public/templates/template-karyawan.xlsx
+++ b/src/public/templates/template-karyawan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a98d17813a983a49/Dokumen/KULIAH/Semester 6 - TI/Magang/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="8_{47ABF467-4E69-4F47-9EF2-98C282960974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E72998E9-6AEE-497B-9B17-2123B959DF92}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="13_ncr:1_{DD9FF5F7-A1D4-4376-A9BA-2C5D6A485E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D6ECF70-5D7D-4708-AAB2-7A14786380F9}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
   <si>
     <t>id_karyawan</t>
   </si>
@@ -76,15 +76,6 @@
     <t>proyek</t>
   </si>
   <si>
-    <t>gaji_lembur_reguler</t>
-  </si>
-  <si>
-    <t>gaji_lembur_sabtu</t>
-  </si>
-  <si>
-    <t>gaji_lembur_minggu_haribesar</t>
-  </si>
-  <si>
     <t>a</t>
   </si>
   <si>
@@ -107,16 +98,57 @@
   </si>
   <si>
     <t>jenis_proyek</t>
+  </si>
+  <si>
+    <t>gaji_lembur</t>
+  </si>
+  <si>
+    <t>uang_makan_lembur_malam</t>
+  </si>
+  <si>
+    <t>uang_makan_lembur_jalan</t>
+  </si>
+  <si>
+    <t>potongan_bpjs_kesehatan</t>
+  </si>
+  <si>
+    <t>potongan_tenaga_kerja</t>
+  </si>
+  <si>
+    <t>potongan_bpjs_kesehatan_tk</t>
+  </si>
+  <si>
+    <t>faktor_sj</t>
+  </si>
+  <si>
+    <t>faktor_sabtu</t>
+  </si>
+  <si>
+    <t>faktor_minggu</t>
+  </si>
+  <si>
+    <t>faktor_hari_besar</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -142,8 +174,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -450,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="12.41796875" customWidth="1"/>
@@ -460,9 +495,16 @@
     <col min="7" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="25.15625" customWidth="1"/>
     <col min="10" max="10" width="17.47265625" customWidth="1"/>
+    <col min="11" max="11" width="18.5234375" customWidth="1"/>
+    <col min="12" max="12" width="21.7890625" customWidth="1"/>
+    <col min="13" max="13" width="24.734375" customWidth="1"/>
+    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="15" max="15" width="18.05078125" customWidth="1"/>
+    <col min="16" max="16" width="19" customWidth="1"/>
+    <col min="17" max="17" width="20.7890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -476,25 +518,46 @@
         <v>13</v>
       </c>
       <c r="E1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" t="s">
         <v>28</v>
       </c>
-      <c r="F1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J1" t="s">
-        <v>3</v>
+      <c r="K1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A2">
         <v>238</v>
       </c>
@@ -508,7 +571,7 @@
         <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F2">
         <v>2600000</v>
@@ -517,16 +580,37 @@
         <v>26000</v>
       </c>
       <c r="H2">
-        <v>35000</v>
+        <v>33000</v>
       </c>
       <c r="I2">
-        <v>50000</v>
+        <v>15000</v>
       </c>
       <c r="J2">
-        <v>33000</v>
+        <v>25000</v>
+      </c>
+      <c r="K2">
+        <v>49000</v>
+      </c>
+      <c r="L2">
+        <v>147000</v>
+      </c>
+      <c r="M2">
+        <v>196000</v>
+      </c>
+      <c r="N2">
+        <v>1.5</v>
+      </c>
+      <c r="O2">
+        <v>1.5</v>
+      </c>
+      <c r="P2">
+        <v>2</v>
+      </c>
+      <c r="Q2">
+        <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
         <v>239</v>
       </c>
@@ -540,7 +624,7 @@
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F3">
         <v>2600001</v>
@@ -549,16 +633,37 @@
         <v>26000</v>
       </c>
       <c r="H3">
-        <v>35000</v>
+        <v>33000</v>
       </c>
       <c r="I3">
-        <v>50000</v>
+        <v>15000</v>
       </c>
       <c r="J3">
-        <v>33001</v>
+        <v>25000</v>
+      </c>
+      <c r="K3">
+        <v>49000</v>
+      </c>
+      <c r="L3">
+        <v>147000</v>
+      </c>
+      <c r="M3">
+        <v>196000</v>
+      </c>
+      <c r="N3">
+        <v>1.5</v>
+      </c>
+      <c r="O3">
+        <v>1.5</v>
+      </c>
+      <c r="P3">
+        <v>2</v>
+      </c>
+      <c r="Q3">
+        <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>240</v>
       </c>
@@ -572,7 +677,7 @@
         <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>2600002</v>
@@ -581,16 +686,37 @@
         <v>26000</v>
       </c>
       <c r="H4">
-        <v>35000</v>
+        <v>33000</v>
       </c>
       <c r="I4">
-        <v>50000</v>
+        <v>15000</v>
       </c>
       <c r="J4">
-        <v>33002</v>
+        <v>25000</v>
+      </c>
+      <c r="K4">
+        <v>49000</v>
+      </c>
+      <c r="L4">
+        <v>147000</v>
+      </c>
+      <c r="M4">
+        <v>196000</v>
+      </c>
+      <c r="N4">
+        <v>1.5</v>
+      </c>
+      <c r="O4">
+        <v>1.5</v>
+      </c>
+      <c r="P4">
+        <v>2</v>
+      </c>
+      <c r="Q4">
+        <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>241</v>
       </c>
@@ -604,7 +730,7 @@
         <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F5">
         <v>2600003</v>
@@ -613,16 +739,37 @@
         <v>26000</v>
       </c>
       <c r="H5">
-        <v>35000</v>
+        <v>33000</v>
       </c>
       <c r="I5">
-        <v>50000</v>
+        <v>15000</v>
       </c>
       <c r="J5">
-        <v>33003</v>
+        <v>25000</v>
+      </c>
+      <c r="K5">
+        <v>49000</v>
+      </c>
+      <c r="L5">
+        <v>147000</v>
+      </c>
+      <c r="M5">
+        <v>196000</v>
+      </c>
+      <c r="N5">
+        <v>1.5</v>
+      </c>
+      <c r="O5">
+        <v>1.5</v>
+      </c>
+      <c r="P5">
+        <v>2</v>
+      </c>
+      <c r="Q5">
+        <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
         <v>242</v>
       </c>
@@ -636,7 +783,7 @@
         <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F6">
         <v>2600004</v>
@@ -645,16 +792,37 @@
         <v>26000</v>
       </c>
       <c r="H6">
-        <v>35000</v>
+        <v>33000</v>
       </c>
       <c r="I6">
-        <v>50000</v>
+        <v>15000</v>
       </c>
       <c r="J6">
-        <v>33004</v>
+        <v>25000</v>
+      </c>
+      <c r="K6">
+        <v>49000</v>
+      </c>
+      <c r="L6">
+        <v>147000</v>
+      </c>
+      <c r="M6">
+        <v>196000</v>
+      </c>
+      <c r="N6">
+        <v>1.5</v>
+      </c>
+      <c r="O6">
+        <v>1.5</v>
+      </c>
+      <c r="P6">
+        <v>2</v>
+      </c>
+      <c r="Q6">
+        <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
         <v>243</v>
       </c>
@@ -668,7 +836,7 @@
         <v>17</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F7">
         <v>2600005</v>
@@ -677,16 +845,37 @@
         <v>26000</v>
       </c>
       <c r="H7">
-        <v>35000</v>
+        <v>33000</v>
       </c>
       <c r="I7">
-        <v>50000</v>
+        <v>15000</v>
       </c>
       <c r="J7">
-        <v>33005</v>
+        <v>25000</v>
+      </c>
+      <c r="K7">
+        <v>49000</v>
+      </c>
+      <c r="L7">
+        <v>147000</v>
+      </c>
+      <c r="M7">
+        <v>196000</v>
+      </c>
+      <c r="N7">
+        <v>1.5</v>
+      </c>
+      <c r="O7">
+        <v>1.5</v>
+      </c>
+      <c r="P7">
+        <v>2</v>
+      </c>
+      <c r="Q7">
+        <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>244</v>
       </c>
@@ -700,7 +889,7 @@
         <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F8">
         <v>2600006</v>
@@ -709,16 +898,39 @@
         <v>26000</v>
       </c>
       <c r="H8">
-        <v>35000</v>
+        <v>33000</v>
       </c>
       <c r="I8">
-        <v>50000</v>
+        <v>15000</v>
       </c>
       <c r="J8">
-        <v>33006</v>
+        <v>25000</v>
+      </c>
+      <c r="K8">
+        <v>49000</v>
+      </c>
+      <c r="L8">
+        <v>147000</v>
+      </c>
+      <c r="M8">
+        <v>196000</v>
+      </c>
+      <c r="N8">
+        <v>1.5</v>
+      </c>
+      <c r="O8">
+        <v>1.5</v>
+      </c>
+      <c r="P8">
+        <v>2</v>
+      </c>
+      <c r="Q8">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
--- a/src/public/templates/template-karyawan.xlsx
+++ b/src/public/templates/template-karyawan.xlsx
@@ -1,26 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a98d17813a983a49/Dokumen/KULIAH/Semester 6 - TI/Magang/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a98d17813a983a49/Dokumen/KULIAH/Semester 6 - TI/testing/real/ekspor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="13_ncr:1_{DD9FF5F7-A1D4-4376-A9BA-2C5D6A485E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D6ECF70-5D7D-4708-AAB2-7A14786380F9}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{85E9F38F-E914-4797-BE3E-EA374C6A511A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53EE945E-C844-45EF-B998-41CB913412B3}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Karyawan" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="27">
   <si>
     <t>id_karyawan</t>
   </si>
@@ -28,113 +39,90 @@
     <t>nama</t>
   </si>
   <si>
-    <t>gaji_perbulan</t>
-  </si>
-  <si>
     <t>gaji_harian</t>
   </si>
   <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>lokasi</t>
+  </si>
+  <si>
+    <t>jenis_proyek</t>
+  </si>
+  <si>
+    <t>gaji_lembur</t>
+  </si>
+  <si>
+    <t>uang_makan_lembur_malam</t>
+  </si>
+  <si>
+    <t>uang_makan_lembur_jalan</t>
+  </si>
+  <si>
+    <t>potongan_bpjs_kesehatan</t>
+  </si>
+  <si>
+    <t>potongan_tenaga_kerja</t>
+  </si>
+  <si>
+    <t>potongan_bpjs_kesehatan_tk</t>
+  </si>
+  <si>
+    <t>faktor_sj</t>
+  </si>
+  <si>
+    <t>faktor_sabtu</t>
+  </si>
+  <si>
+    <t>faktor_minggu</t>
+  </si>
+  <si>
+    <t>faktor_hari_besar</t>
+  </si>
+  <si>
     <t>harian tetap</t>
   </si>
   <si>
-    <t>kodi</t>
-  </si>
-  <si>
-    <t>koda</t>
-  </si>
-  <si>
-    <t>kodu</t>
-  </si>
-  <si>
-    <t>jumbo</t>
-  </si>
-  <si>
-    <t>adit</t>
-  </si>
-  <si>
-    <t>sopo</t>
-  </si>
-  <si>
-    <t>jarwo</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>lokasi</t>
+    <t>harian lepas</t>
   </si>
   <si>
     <t>workshop</t>
   </si>
   <si>
-    <t>harian lepas</t>
-  </si>
-  <si>
-    <t>staff</t>
-  </si>
-  <si>
-    <t>proyek</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>d</t>
-  </si>
-  <si>
-    <t>e</t>
-  </si>
-  <si>
-    <t>f</t>
-  </si>
-  <si>
-    <t>g</t>
-  </si>
-  <si>
-    <t>jenis_proyek</t>
-  </si>
-  <si>
-    <t>gaji_lembur</t>
-  </si>
-  <si>
-    <t>uang_makan_lembur_malam</t>
-  </si>
-  <si>
-    <t>uang_makan_lembur_jalan</t>
-  </si>
-  <si>
-    <t>potongan_bpjs_kesehatan</t>
-  </si>
-  <si>
-    <t>potongan_tenaga_kerja</t>
-  </si>
-  <si>
-    <t>potongan_bpjs_kesehatan_tk</t>
-  </si>
-  <si>
-    <t>faktor_sj</t>
-  </si>
-  <si>
-    <t>faktor_sabtu</t>
-  </si>
-  <si>
-    <t>faktor_minggu</t>
-  </si>
-  <si>
-    <t>faktor_hari_besar</t>
+    <t>bagian</t>
+  </si>
+  <si>
+    <t>logistik</t>
+  </si>
+  <si>
+    <t>sutiandi wijaya</t>
+  </si>
+  <si>
+    <t>agus suhaedi</t>
+  </si>
+  <si>
+    <t>ahmad haerul fadlan</t>
+  </si>
+  <si>
+    <t>rian adriansyah</t>
+  </si>
+  <si>
+    <t>logistik (solar)</t>
+  </si>
+  <si>
+    <t>gaji_setengah_bulan</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -152,6 +140,16 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -171,8 +169,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -180,8 +184,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="7">
+    <cellStyle name="Comma [0] 2" xfId="6" xr:uid="{5A5AD55D-9758-4CA1-A549-F304D1552A14}"/>
+    <cellStyle name="Comma [0] 3" xfId="4" xr:uid="{8EC76E2F-3CA3-4A5B-B93F-9C96149F7F90}"/>
+    <cellStyle name="Comma 2" xfId="5" xr:uid="{B908A148-CB1B-4AFB-82AA-72D424DB055C}"/>
+    <cellStyle name="Comma 3" xfId="3" xr:uid="{BD72645A-8F39-4787-A8EF-4BBB4C2FA7E6}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{F446AC89-53B9-4E30-9AD3-05CEA432AEEA}"/>
+    <cellStyle name="Normal 2 2" xfId="1" xr:uid="{1299B49A-5A68-42D2-AC8F-CE414ADC5520}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -194,10 +204,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -485,26 +491,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:R5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.41796875" customWidth="1"/>
-    <col min="3" max="3" width="10.26171875" customWidth="1"/>
-    <col min="4" max="5" width="11.3125" customWidth="1"/>
-    <col min="6" max="6" width="16.68359375" customWidth="1"/>
-    <col min="7" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="25.15625" customWidth="1"/>
-    <col min="10" max="10" width="17.47265625" customWidth="1"/>
-    <col min="11" max="11" width="18.5234375" customWidth="1"/>
-    <col min="12" max="12" width="21.7890625" customWidth="1"/>
-    <col min="13" max="13" width="24.734375" customWidth="1"/>
-    <col min="14" max="14" width="14" customWidth="1"/>
-    <col min="15" max="15" width="18.05078125" customWidth="1"/>
-    <col min="16" max="16" width="19" customWidth="1"/>
-    <col min="17" max="17" width="20.7890625" customWidth="1"/>
+    <col min="2" max="2" width="20.68359375" customWidth="1"/>
+    <col min="3" max="3" width="12.41796875" customWidth="1"/>
+    <col min="4" max="4" width="11.26171875" customWidth="1"/>
+    <col min="5" max="5" width="13.26171875" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="16.68359375" customWidth="1"/>
+    <col min="8" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="25.15625" customWidth="1"/>
+    <col min="11" max="11" width="17.41796875" customWidth="1"/>
+    <col min="12" max="12" width="18.578125" customWidth="1"/>
+    <col min="13" max="13" width="21.83984375" customWidth="1"/>
+    <col min="14" max="14" width="24.68359375" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="16" max="16" width="18" customWidth="1"/>
+    <col min="17" max="17" width="19" customWidth="1"/>
+    <col min="18" max="18" width="20.83984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -512,419 +521,239 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
         <v>26</v>
       </c>
       <c r="H1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I1" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="J1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>29</v>
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
+        <v>8</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>35</v>
+        <v>14</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:18">
       <c r="A2">
-        <v>238</v>
+        <v>112</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" t="s">
         <v>18</v>
       </c>
-      <c r="F2">
-        <v>2600000</v>
-      </c>
       <c r="G2">
-        <v>26000</v>
+        <v>2375000</v>
       </c>
       <c r="H2">
-        <v>33000</v>
-      </c>
-      <c r="I2">
+        <v>26023</v>
+      </c>
+      <c r="J2">
         <v>15000</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>25000</v>
       </c>
-      <c r="K2">
-        <v>49000</v>
-      </c>
-      <c r="L2">
-        <v>147000</v>
-      </c>
-      <c r="M2">
+      <c r="N2">
         <v>196000</v>
-      </c>
-      <c r="N2">
-        <v>1.5</v>
       </c>
       <c r="O2">
         <v>1.5</v>
       </c>
       <c r="P2">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Q2">
         <v>2</v>
       </c>
+      <c r="R2">
+        <v>2</v>
+      </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:18">
       <c r="A3">
-        <v>239</v>
+        <v>152</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3">
-        <v>2600001</v>
-      </c>
-      <c r="G3">
-        <v>26000</v>
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
       </c>
       <c r="H3">
-        <v>33000</v>
+        <v>23125</v>
       </c>
       <c r="I3">
+        <v>185000</v>
+      </c>
+      <c r="J3">
         <v>15000</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>25000</v>
       </c>
-      <c r="K3">
-        <v>49000</v>
-      </c>
-      <c r="L3">
-        <v>147000</v>
-      </c>
-      <c r="M3">
+      <c r="N3">
         <v>196000</v>
-      </c>
-      <c r="N3">
-        <v>1.5</v>
       </c>
       <c r="O3">
         <v>1.5</v>
       </c>
       <c r="P3">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Q3">
         <v>2</v>
       </c>
+      <c r="R3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:18">
       <c r="A4">
-        <v>240</v>
+        <v>185</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
       </c>
-      <c r="F4">
-        <v>2600002</v>
-      </c>
-      <c r="G4">
-        <v>26000</v>
+      <c r="F4" t="s">
+        <v>18</v>
       </c>
       <c r="H4">
-        <v>33000</v>
+        <v>21875</v>
       </c>
       <c r="I4">
+        <v>175000</v>
+      </c>
+      <c r="J4">
         <v>15000</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>25000</v>
       </c>
-      <c r="K4">
-        <v>49000</v>
-      </c>
-      <c r="L4">
-        <v>147000</v>
-      </c>
-      <c r="M4">
+      <c r="N4">
         <v>196000</v>
-      </c>
-      <c r="N4">
-        <v>1.5</v>
       </c>
       <c r="O4">
         <v>1.5</v>
       </c>
       <c r="P4">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Q4">
         <v>2</v>
       </c>
+      <c r="R4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:18">
       <c r="A5">
-        <v>241</v>
+        <v>148</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>2600003</v>
-      </c>
-      <c r="G5">
-        <v>26000</v>
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
       </c>
       <c r="H5">
-        <v>33000</v>
+        <v>21875</v>
       </c>
       <c r="I5">
+        <v>175000</v>
+      </c>
+      <c r="J5">
         <v>15000</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>25000</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>49000</v>
-      </c>
-      <c r="L5">
-        <v>147000</v>
-      </c>
-      <c r="M5">
-        <v>196000</v>
-      </c>
-      <c r="N5">
-        <v>1.5</v>
       </c>
       <c r="O5">
         <v>1.5</v>
       </c>
       <c r="P5">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Q5">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6">
-        <v>242</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6">
-        <v>2600004</v>
-      </c>
-      <c r="G6">
-        <v>26000</v>
-      </c>
-      <c r="H6">
-        <v>33000</v>
-      </c>
-      <c r="I6">
-        <v>15000</v>
-      </c>
-      <c r="J6">
-        <v>25000</v>
-      </c>
-      <c r="K6">
-        <v>49000</v>
-      </c>
-      <c r="L6">
-        <v>147000</v>
-      </c>
-      <c r="M6">
-        <v>196000</v>
-      </c>
-      <c r="N6">
-        <v>1.5</v>
-      </c>
-      <c r="O6">
-        <v>1.5</v>
-      </c>
-      <c r="P6">
-        <v>2</v>
-      </c>
-      <c r="Q6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7">
-        <v>243</v>
-      </c>
-      <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7">
-        <v>2600005</v>
-      </c>
-      <c r="G7">
-        <v>26000</v>
-      </c>
-      <c r="H7">
-        <v>33000</v>
-      </c>
-      <c r="I7">
-        <v>15000</v>
-      </c>
-      <c r="J7">
-        <v>25000</v>
-      </c>
-      <c r="K7">
-        <v>49000</v>
-      </c>
-      <c r="L7">
-        <v>147000</v>
-      </c>
-      <c r="M7">
-        <v>196000</v>
-      </c>
-      <c r="N7">
-        <v>1.5</v>
-      </c>
-      <c r="O7">
-        <v>1.5</v>
-      </c>
-      <c r="P7">
-        <v>2</v>
-      </c>
-      <c r="Q7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8">
-        <v>244</v>
-      </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8">
-        <v>2600006</v>
-      </c>
-      <c r="G8">
-        <v>26000</v>
-      </c>
-      <c r="H8">
-        <v>33000</v>
-      </c>
-      <c r="I8">
-        <v>15000</v>
-      </c>
-      <c r="J8">
-        <v>25000</v>
-      </c>
-      <c r="K8">
-        <v>49000</v>
-      </c>
-      <c r="L8">
-        <v>147000</v>
-      </c>
-      <c r="M8">
-        <v>196000</v>
-      </c>
-      <c r="N8">
-        <v>1.5</v>
-      </c>
-      <c r="O8">
-        <v>1.5</v>
-      </c>
-      <c r="P8">
-        <v>2</v>
-      </c>
-      <c r="Q8">
+      <c r="R5">
         <v>2</v>
       </c>
     </row>
